--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486723_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486723_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8612</v>
+        <v>3.6322</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0943</v>
+        <v>2.6666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7669</v>
+        <v>0.9656</v>
       </c>
       <c r="G2" t="n">
         <v>-0.1306</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9433</v>
+        <v>-0.1724</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9933</v>
+        <v>-0.421</v>
       </c>
       <c r="U2" t="n">
-        <v>0.05</v>
+        <v>0.2486</v>
       </c>
       <c r="V2" t="n">
         <v>2.0044</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7975</v>
+        <v>2.4182</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7074</v>
+        <v>2.4524</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09</v>
+        <v>-0.0341</v>
       </c>
       <c r="G3" t="n">
         <v>2.8044</v>
@@ -688,13 +688,13 @@
         <v>0.9654</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1931</v>
+        <v>-0.1861</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1934</v>
+        <v>-0.4485</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3866</v>
+        <v>0.2624</v>
       </c>
       <c r="V3" t="n">
         <v>-0.7792</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.587</v>
+        <v>1.1634</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2533</v>
+        <v>0.929</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3337</v>
+        <v>0.2344</v>
       </c>
       <c r="G4" t="n">
         <v>0.0418</v>
@@ -766,13 +766,13 @@
         <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8108</v>
+        <v>-0.2344</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.214</v>
+        <v>-0.5383</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4032</v>
+        <v>0.3039</v>
       </c>
       <c r="V4" t="n">
         <v>0.7766999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.6222</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3358</v>
+        <v>-1.2114</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2415</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9226</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7278</v>
+        <v>0.1998</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1579</v>
+        <v>0.2823</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4301</v>
+        <v>-0.0824</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2856</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0306</v>
+        <v>-0.9809</v>
       </c>
       <c r="E6" t="n">
         <v>0.9849</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0155</v>
+        <v>-1.9658</v>
       </c>
       <c r="G6" t="n">
         <v>0.4674</v>
@@ -922,13 +922,13 @@
         <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2703</v>
+        <v>-0.2207</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1048</v>
+        <v>-0.0551</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2277</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>J. HERRERO ALONSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3612</v>
+        <v>-1.441</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1662</v>
+        <v>-1.9718</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.195</v>
+        <v>0.5308</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6147</v>
+        <v>-4.4817</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-1.145</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0557</v>
+        <v>-3.3367</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2762</v>
+        <v>-2.4592</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0621</v>
+        <v>0.3732</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3383</v>
+        <v>-2.8324</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3385</v>
+        <v>-2.0225</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6211</v>
+        <v>-1.5183</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2826</v>
+        <v>-0.5042</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1931</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1931</v>
+        <v>2.3169</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0605</v>
+        <v>-0.2759</v>
       </c>
       <c r="T7" t="n">
-        <v>0.11</v>
+        <v>-0.635</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0495</v>
+        <v>0.3591</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>4.0889</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>4.2117</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7318</v>
+        <v>-1.4976</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-1.4764</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.821</v>
+        <v>-0.0212</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2145</v>
+        <v>-1.6147</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0276</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1868</v>
+        <v>-1.0557</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-1.2762</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0414</v>
+        <v>0.0621</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6488</v>
+        <v>-1.3383</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6071</v>
+        <v>-0.3385</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.6211</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5381</v>
+        <v>0.2826</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2317</v>
+        <v>-0.076</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1104</v>
+        <v>-0.2003</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1213</v>
+        <v>0.1243</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. LUIS HERRERA</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8573</v>
+        <v>-1.707</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7006</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8433</v>
+        <v>-0.7961</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6807</v>
+        <v>-1.2145</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.71</v>
+        <v>-0.0276</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0294</v>
+        <v>-1.1868</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.328</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0198</v>
+        <v>0.0414</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6918</v>
+        <v>-0.6488</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3527</v>
+        <v>-0.6071</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6903</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6624</v>
+        <v>-0.5381</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8962</v>
+        <v>-0.1931</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1749</v>
+        <v>-0.2069</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5236</v>
+        <v>-0.1104</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6513</v>
+        <v>-0.0965</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. HERRERO ALONSO</t>
+          <t>N. LUIS HERRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5222</v>
+        <v>-2.4945</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8543</v>
+        <v>-3.1143</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3321</v>
+        <v>0.6198</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.4817</v>
+        <v>-1.6807</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.145</v>
+        <v>-1.71</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3367</v>
+        <v>0.0294</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4592</v>
+        <v>-0.328</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3732</v>
+        <v>-1.0198</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.8324</v>
+        <v>0.6918</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0225</v>
+        <v>-1.3527</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5183</v>
+        <v>-0.6903</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5042</v>
+        <v>-0.6624</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7723</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0892</v>
+        <v>-2.8962</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3169</v>
+        <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3571</v>
+        <v>0.5377</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5176</v>
+        <v>0.1099</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1604</v>
+        <v>0.4278</v>
       </c>
       <c r="V10" t="n">
-        <v>4.0889</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>4.2117</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7801</v>
+        <v>-6.3264</v>
       </c>
       <c r="E11" t="n">
         <v>-6.1182</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3381</v>
+        <v>-0.2082</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8562</v>
@@ -1312,13 +1312,13 @@
         <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7669</v>
+        <v>0.2206</v>
       </c>
       <c r="T11" t="n">
         <v>-0.497</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2638</v>
+        <v>0.7175</v>
       </c>
       <c r="V11" t="n">
         <v>0.8193</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.1318</v>
+        <v>-7.8558</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.045999999999999</v>
+        <v>-7.77</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.08589999999999975</v>
+        <v>-0.08560000000000006</v>
       </c>
       <c r="G12" t="n">
         <v>-11.5874</v>
@@ -1360,16 +1360,16 @@
         <v>-4.8278</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.7594</v>
+        <v>-6.759400000000001</v>
       </c>
       <c r="J12" t="n">
         <v>1.216</v>
       </c>
       <c r="K12" t="n">
-        <v>2.764099999999999</v>
+        <v>2.7641</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.548</v>
+        <v>-1.547999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-12.8034</v>
@@ -1378,10 +1378,10 @@
         <v>-7.5921</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.211399999999999</v>
+        <v>-5.2114</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9652999999999992</v>
+        <v>-0.9652999999999994</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.5155</v>
@@ -1390,10 +1390,10 @@
         <v>12.55</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6899999999999998</v>
+        <v>-0.4143000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.8997</v>
+        <v>-2.6238</v>
       </c>
       <c r="U12" t="n">
         <v>2.2096</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0958</v>
+        <v>4.7041</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4292</v>
+        <v>1.2224</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6666</v>
+        <v>3.4817</v>
       </c>
       <c r="G13" t="n">
         <v>6.8278</v>
@@ -1468,13 +1468,13 @@
         <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>0.585</v>
+        <v>0.1932</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.359</v>
+        <v>-0.5658</v>
       </c>
       <c r="U13" t="n">
-        <v>0.944</v>
+        <v>0.7591</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARÍN REYES</t>
+          <t>A. GUERRERO PAEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4171</v>
+        <v>3.7205</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5354</v>
+        <v>0.4388</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8817</v>
+        <v>3.2817</v>
       </c>
       <c r="G14" t="n">
-        <v>4.9449</v>
+        <v>2.2557</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4205</v>
+        <v>0.7997</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5244</v>
+        <v>1.456</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8288</v>
+        <v>1.1396</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7316</v>
+        <v>0.1109</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0972</v>
+        <v>1.0287</v>
       </c>
       <c r="M14" t="n">
         <v>1.1161</v>
@@ -1537,37 +1537,37 @@
         <v>0.4272</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1585</v>
+        <v>1.7377</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0892</v>
+        <v>-0.1931</v>
       </c>
       <c r="R14" t="n">
         <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3694</v>
+        <v>-0.5586</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1036</v>
+        <v>-0.7934</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7343</v>
+        <v>0.2348</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8995</v>
+        <v>0.2856</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GUERRERO PAEZ</t>
+          <t>A. MARÍN REYES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,31 +1579,31 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7508</v>
+        <v>3.6417</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1285</v>
+        <v>0.8457</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6223</v>
+        <v>2.7961</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2557</v>
+        <v>4.9449</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7997</v>
+        <v>1.4205</v>
       </c>
       <c r="I15" t="n">
-        <v>1.456</v>
+        <v>3.5244</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1396</v>
+        <v>3.8288</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1109</v>
+        <v>0.7316</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0287</v>
+        <v>3.0972</v>
       </c>
       <c r="M15" t="n">
         <v>1.1161</v>
@@ -1615,31 +1615,31 @@
         <v>0.4272</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7377</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1931</v>
+        <v>-3.0892</v>
       </c>
       <c r="R15" t="n">
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5282</v>
+        <v>-0.1447</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1036</v>
+        <v>-0.7934</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4245</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2856</v>
+        <v>0.8995</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2484</v>
+        <v>1.9353</v>
       </c>
       <c r="E16" t="n">
-        <v>2.067</v>
+        <v>2.4807</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8186</v>
+        <v>-0.5454</v>
       </c>
       <c r="G16" t="n">
         <v>1.2043</v>
@@ -1702,13 +1702,13 @@
         <v>0.7723</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5351</v>
+        <v>0.1517</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3036</v>
+        <v>0.1101</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2316</v>
+        <v>0.0416</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>A. RELAÑO LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7482</v>
+        <v>0.3777</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0879</v>
+        <v>1.9041</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3397</v>
+        <v>-1.5263</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4153</v>
+        <v>1.4938</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2616</v>
+        <v>1.3175</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1537</v>
+        <v>0.1763</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4012</v>
+        <v>2.722</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0545</v>
+        <v>2.5592</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6534</v>
+        <v>0.1628</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0142</v>
+        <v>-1.2282</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2071</v>
+        <v>-1.2417</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8071</v>
+        <v>0.0135</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3862</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>2.063</v>
+        <v>0.2621</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6822</v>
+        <v>0.0549</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3808</v>
+        <v>0.2071</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2856</v>
+        <v>-1.1851</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2856</v>
+        <v>-1.4707</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RELAÑO LOPEZ</t>
+          <t>A. BARBEITO RUIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0882</v>
+        <v>0.1003</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4904</v>
+        <v>-0.2643</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4022</v>
+        <v>0.3647</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4938</v>
+        <v>-0.8996</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3175</v>
+        <v>-2.0277</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1763</v>
+        <v>1.128</v>
       </c>
       <c r="J18" t="n">
-        <v>2.722</v>
+        <v>0.1842</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5592</v>
+        <v>-0.5099</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1628</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2282</v>
+        <v>-1.0838</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2417</v>
+        <v>-1.5178</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0135</v>
+        <v>0.434</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1585</v>
+        <v>-0.3862</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0275</v>
+        <v>0.2276</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3587</v>
+        <v>-0.0624</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3313</v>
+        <v>0.29</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1851</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0242</v>
+        <v>-0.1761</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.5133</v>
+        <v>-3.3064</v>
       </c>
       <c r="F19" t="n">
-        <v>3.4891</v>
+        <v>3.1304</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8794999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2761</v>
+        <v>0.1242</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8277</v>
+        <v>-0.6209</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1039</v>
+        <v>0.7451</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BARBEITO RUIZ</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3423</v>
+        <v>-0.5425</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7815</v>
+        <v>-0.1531</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4392</v>
+        <v>-0.3894</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8996</v>
+        <v>-1.4153</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0277</v>
+        <v>-1.2616</v>
       </c>
       <c r="I20" t="n">
-        <v>1.128</v>
+        <v>-0.1537</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1842</v>
+        <v>-0.4012</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5099</v>
+        <v>-1.0545</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6534</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0838</v>
+        <v>-1.0142</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5178</v>
+        <v>-0.2071</v>
       </c>
       <c r="O20" t="n">
-        <v>0.434</v>
+        <v>-0.8071</v>
       </c>
       <c r="P20" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.1931</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.7723</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.3862</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.1585</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-0.215</v>
-      </c>
       <c r="T20" t="n">
-        <v>-0.5795</v>
+        <v>0.4411</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3645</v>
+        <v>0.3312</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. TERRATS MADRID</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2919</v>
+        <v>-0.619</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6912</v>
+        <v>0.212</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3993</v>
+        <v>-0.831</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1359</v>
+        <v>-1.3266</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5445</v>
+        <v>-0.5241</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6804</v>
+        <v>-0.8025</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.0327</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6821</v>
+        <v>0.7176</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1221</v>
+        <v>-0.6849</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6959</v>
+        <v>-1.3593</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1376</v>
+        <v>-1.2417</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5583</v>
+        <v>-0.1176</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1931</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2206</v>
+        <v>0.1517</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0273</v>
+        <v>0.1101</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1933</v>
+        <v>0.0416</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8415</v>
+        <v>0.9421</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8415</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>R. TERRATS MADRID</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3058</v>
+        <v>-1.7056</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2017</v>
+        <v>-2.1048</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1042</v>
+        <v>0.3993</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3266</v>
+        <v>0.1359</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5241</v>
+        <v>-0.5445</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8025</v>
+        <v>0.6804</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0327</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7176</v>
+        <v>-0.6821</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6849</v>
+        <v>0.1221</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3593</v>
+        <v>0.6959</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2417</v>
+        <v>0.1376</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1176</v>
+        <v>0.5583</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1585</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5351</v>
+        <v>-0.1931</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3036</v>
+        <v>-0.3864</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2316</v>
+        <v>0.1933</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9421</v>
+        <v>-1.8415</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2856</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2526</v>
+        <v>-2.6152</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4652</v>
+        <v>-1.1892</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7874</v>
+        <v>-1.426</v>
       </c>
       <c r="G23" t="n">
         <v>-0.754</v>
@@ -2248,13 +2248,13 @@
         <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7556</v>
+        <v>0.3931</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0202</v>
+        <v>0.2963</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2646</v>
+        <v>0.0968</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0266</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.131700000000002</v>
+        <v>8.821199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08549999999999952</v>
+        <v>0.08590000000000053</v>
       </c>
       <c r="F24" t="n">
-        <v>8.046100000000001</v>
+        <v>8.735799999999999</v>
       </c>
       <c r="G24" t="n">
         <v>11.5874</v>
@@ -2296,7 +2296,7 @@
         <v>4.827800000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>6.759499999999998</v>
+        <v>6.7595</v>
       </c>
       <c r="J24" t="n">
         <v>12.8034</v>
@@ -2317,7 +2317,7 @@
         <v>1.5479</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9653000000000002</v>
+        <v>0.9652999999999998</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.5502</v>
@@ -2326,13 +2326,13 @@
         <v>13.5154</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6900000000000006</v>
+        <v>1.3795</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.2096</v>
+        <v>-2.2098</v>
       </c>
       <c r="U24" t="n">
-        <v>2.8998</v>
+        <v>3.5893</v>
       </c>
       <c r="V24" t="n">
         <v>-5.1111</v>
